--- a/name_list.xlsx
+++ b/name_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8e3e5a1607340544/โรงเรียนบ้านโพนแท่น/Pontan-67/ปริ้นปพ2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Phontan-Chang\Documents\printPorpo2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_F25DC773A252ABDACC10482E219E7E025ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DA20F82-6463-42A2-9334-2550332AEDEF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064DB0CE-1A6E-4561-A3AC-DD4812DD07F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>คำนำหน้า</t>
   </si>
@@ -48,9 +48,6 @@
     <t>นาย</t>
   </si>
   <si>
-    <t>กุมภาพันธ์</t>
-  </si>
-  <si>
     <t>นางสาว</t>
   </si>
   <si>
@@ -63,136 +60,106 @@
     <t>พฤษภาคม</t>
   </si>
   <si>
-    <t>ก้อย</t>
-  </si>
-  <si>
     <t>สิงหาคม</t>
   </si>
   <si>
     <t>กันยายน</t>
   </si>
   <si>
-    <t>พฤศจิกายน</t>
-  </si>
-  <si>
-    <t>ณรงค์ฤทธิ์</t>
-  </si>
-  <si>
-    <t>สมรูป</t>
-  </si>
-  <si>
-    <t>รัฐภูมิ</t>
-  </si>
-  <si>
-    <t>สุทธิกร</t>
-  </si>
-  <si>
-    <t>กฤษณา</t>
-  </si>
-  <si>
-    <t>ประสาธิโก</t>
-  </si>
-  <si>
-    <t>กิตติมา</t>
-  </si>
-  <si>
-    <t>กาไธสง</t>
-  </si>
-  <si>
-    <t>กัญญณัท</t>
-  </si>
-  <si>
-    <t>รุ่งเรือง</t>
-  </si>
-  <si>
-    <t>ทิพย์สุดา</t>
-  </si>
-  <si>
-    <t>จ่าฮึม</t>
-  </si>
-  <si>
-    <t>ภูริวัฒน์</t>
-  </si>
-  <si>
-    <t>แก้วประไพ</t>
-  </si>
-  <si>
-    <t>วรรณะ</t>
-  </si>
-  <si>
-    <t>ฐดาภา</t>
-  </si>
-  <si>
-    <t>ดุมา</t>
-  </si>
-  <si>
-    <t>อัศวิน</t>
-  </si>
-  <si>
-    <t>เจือจันทร์</t>
-  </si>
-  <si>
-    <t>เมษายน</t>
-  </si>
-  <si>
-    <t>วีรภัทร</t>
-  </si>
-  <si>
-    <t>เกตุชมภู</t>
-  </si>
-  <si>
-    <t>มาริษา</t>
-  </si>
-  <si>
-    <t>แปวประเสริฐ</t>
-  </si>
-  <si>
-    <t>ทยาวัตร์</t>
-  </si>
-  <si>
-    <t>พงษ์เฉลียว</t>
-  </si>
-  <si>
     <t>เลขที่</t>
   </si>
   <si>
-    <t>1/2567</t>
-  </si>
-  <si>
-    <t>2/2567</t>
-  </si>
-  <si>
-    <t>13/2567</t>
-  </si>
-  <si>
-    <t>3/2567</t>
-  </si>
-  <si>
-    <t>4/2567</t>
-  </si>
-  <si>
-    <t>5/2567</t>
-  </si>
-  <si>
-    <t>6/2567</t>
-  </si>
-  <si>
-    <t>7/2567</t>
-  </si>
-  <si>
-    <t>8/2567</t>
-  </si>
-  <si>
-    <t>9/2567</t>
-  </si>
-  <si>
-    <t>10/2567</t>
-  </si>
-  <si>
-    <t>11/2567</t>
-  </si>
-  <si>
-    <t>12/2567</t>
+    <t>1/2569</t>
+  </si>
+  <si>
+    <t>2/2569</t>
+  </si>
+  <si>
+    <t>3/2569</t>
+  </si>
+  <si>
+    <t>4/2569</t>
+  </si>
+  <si>
+    <t>5/2569</t>
+  </si>
+  <si>
+    <t>6/2569</t>
+  </si>
+  <si>
+    <t>7/2569</t>
+  </si>
+  <si>
+    <t>8/2569</t>
+  </si>
+  <si>
+    <t>9/2569</t>
+  </si>
+  <si>
+    <t>10/2569</t>
+  </si>
+  <si>
+    <t>วีรภาพ</t>
+  </si>
+  <si>
+    <t>ศรีสอน</t>
+  </si>
+  <si>
+    <t>วรินทร</t>
+  </si>
+  <si>
+    <t>กิตติศักดิ์</t>
+  </si>
+  <si>
+    <t>คงสุดี</t>
+  </si>
+  <si>
+    <t>สืบศักดิ์</t>
+  </si>
+  <si>
+    <t>เสริมวิเศษ</t>
+  </si>
+  <si>
+    <t>กมลชนก</t>
+  </si>
+  <si>
+    <t>ลิ้มวดี</t>
+  </si>
+  <si>
+    <t>สุกานต์ดา</t>
+  </si>
+  <si>
+    <t>สินนุบุรีรัมย์</t>
+  </si>
+  <si>
+    <t>สุชาดา</t>
+  </si>
+  <si>
+    <t>ซาภู</t>
+  </si>
+  <si>
+    <t>นราธร</t>
+  </si>
+  <si>
+    <t>ผุยหัวโทน</t>
+  </si>
+  <si>
+    <t>สุกัญญา</t>
+  </si>
+  <si>
+    <t>มิสา</t>
+  </si>
+  <si>
+    <t>วิศวกร</t>
+  </si>
+  <si>
+    <t>เผยศิริ</t>
+  </si>
+  <si>
+    <t>มกราคม</t>
+  </si>
+  <si>
+    <t>วงทิพย์</t>
   </si>
 </sst>
 </file>
@@ -203,7 +170,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -512,16 +479,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -542,304 +509,244 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G2">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="G3">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E4">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9">
-        <v>2553</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10">
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11">
         <v>5</v>
       </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="F11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
       <c r="G11">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12">
-        <v>26</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14">
-        <v>2552</v>
-      </c>
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
